--- a/Results/ClinVar/gene_level/top_decile_genes_across_plm_backgrounds.xlsx
+++ b/Results/ClinVar/gene_level/top_decile_genes_across_plm_backgrounds.xlsx
@@ -1,37 +1,414 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+  <si>
+    <t>gene</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>n_pathogenic</t>
+  </si>
+  <si>
+    <t>n_benign</t>
+  </si>
+  <si>
+    <t>esm2_calm_weight</t>
+  </si>
+  <si>
+    <t>esm2_codon_rank</t>
+  </si>
+  <si>
+    <t>esm2_top_codon_weight_decile</t>
+  </si>
+  <si>
+    <t>esm2_cross_modal_gain</t>
+  </si>
+  <si>
+    <t>esm2_gain_rank</t>
+  </si>
+  <si>
+    <t>esm2_top_cross_modal_gain_decile</t>
+  </si>
+  <si>
+    <t>esm1b_calm_weight</t>
+  </si>
+  <si>
+    <t>esm1b_codon_rank</t>
+  </si>
+  <si>
+    <t>esm1b_top_codon_weight_decile</t>
+  </si>
+  <si>
+    <t>esm1b_gain_over_protein</t>
+  </si>
+  <si>
+    <t>esm1b_gain_rank</t>
+  </si>
+  <si>
+    <t>esm1b_top_gain_decile</t>
+  </si>
+  <si>
+    <t>top_weight_both_plm_backgrounds</t>
+  </si>
+  <si>
+    <t>top_weight_and_gain_within_esm2</t>
+  </si>
+  <si>
+    <t>SH3BP2</t>
+  </si>
+  <si>
+    <t>MEF2C</t>
+  </si>
+  <si>
+    <t>GP1BA</t>
+  </si>
+  <si>
+    <t>MMACHC</t>
+  </si>
+  <si>
+    <t>KCNH1</t>
+  </si>
+  <si>
+    <t>SOX5</t>
+  </si>
+  <si>
+    <t>SOX9</t>
+  </si>
+  <si>
+    <t>ADGRG1</t>
+  </si>
+  <si>
+    <t>MLH1</t>
+  </si>
+  <si>
+    <t>GATA1</t>
+  </si>
+  <si>
+    <t>UROS</t>
+  </si>
+  <si>
+    <t>STING1</t>
+  </si>
+  <si>
+    <t>FGFR3</t>
+  </si>
+  <si>
+    <t>PAFAH1B1</t>
+  </si>
+  <si>
+    <t>COL6A2</t>
+  </si>
+  <si>
+    <t>ROBO4</t>
+  </si>
+  <si>
+    <t>MLC1</t>
+  </si>
+  <si>
+    <t>POT1</t>
+  </si>
+  <si>
+    <t>EMD</t>
+  </si>
+  <si>
+    <t>FOXG1</t>
+  </si>
+  <si>
+    <t>IRF2BPL</t>
+  </si>
+  <si>
+    <t>FOXP3</t>
+  </si>
+  <si>
+    <t>TFE3</t>
+  </si>
+  <si>
+    <t>FH</t>
+  </si>
+  <si>
+    <t>EZH2</t>
+  </si>
+  <si>
+    <t>PTPN11</t>
+  </si>
+  <si>
+    <t>PDE4D</t>
+  </si>
+  <si>
+    <t>AFG3L2</t>
+  </si>
+  <si>
+    <t>ASL</t>
+  </si>
+  <si>
+    <t>CNOT3</t>
+  </si>
+  <si>
+    <t>PCYT1A</t>
+  </si>
+  <si>
+    <t>RALA</t>
+  </si>
+  <si>
+    <t>PRKAG2</t>
+  </si>
+  <si>
+    <t>RLIM</t>
+  </si>
+  <si>
+    <t>GARS1</t>
+  </si>
+  <si>
+    <t>GPR143</t>
+  </si>
+  <si>
+    <t>GFAP</t>
+  </si>
+  <si>
+    <t>CYP11B2</t>
+  </si>
+  <si>
+    <t>COL10A1</t>
+  </si>
+  <si>
+    <t>SPAST</t>
+  </si>
+  <si>
+    <t>TUBB2A</t>
+  </si>
+  <si>
+    <t>SLC6A1</t>
+  </si>
+  <si>
+    <t>SPG7</t>
+  </si>
+  <si>
+    <t>GNAO1</t>
+  </si>
+  <si>
+    <t>SRD5A2</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>WDR45</t>
+  </si>
+  <si>
+    <t>MMUT</t>
+  </si>
+  <si>
+    <t>PORCN</t>
+  </si>
+  <si>
+    <t>MSH2</t>
+  </si>
+  <si>
+    <t>ALAS2</t>
+  </si>
+  <si>
+    <t>FOXH1</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>KIF22</t>
+  </si>
+  <si>
+    <t>OPA1</t>
+  </si>
+  <si>
+    <t>CNGB3</t>
+  </si>
+  <si>
+    <t>MTHFR</t>
+  </si>
+  <si>
+    <t>GATA2</t>
+  </si>
+  <si>
+    <t>KRIT1</t>
+  </si>
+  <si>
+    <t>DCLRE1C</t>
+  </si>
+  <si>
+    <t>PDE6C</t>
+  </si>
+  <si>
+    <t>PADI6</t>
+  </si>
+  <si>
+    <t>GLDC</t>
+  </si>
+  <si>
+    <t>LHCGR</t>
+  </si>
+  <si>
+    <t>PRSS1</t>
+  </si>
+  <si>
+    <t>GRIN1</t>
+  </si>
+  <si>
+    <t>TP63</t>
+  </si>
+  <si>
+    <t>CAMK2B</t>
+  </si>
+  <si>
+    <t>PPP2R5D</t>
+  </si>
+  <si>
+    <t>EPHB4</t>
+  </si>
+  <si>
+    <t>IL7R</t>
+  </si>
+  <si>
+    <t>RAG2</t>
+  </si>
+  <si>
+    <t>GPI</t>
+  </si>
+  <si>
+    <t>HBB</t>
+  </si>
+  <si>
+    <t>RPE65</t>
+  </si>
+  <si>
+    <t>DNAI1</t>
+  </si>
+  <si>
+    <t>KCND2</t>
+  </si>
+  <si>
+    <t>CDH1</t>
+  </si>
+  <si>
+    <t>MAK</t>
+  </si>
+  <si>
+    <t>ZMYND11</t>
+  </si>
+  <si>
+    <t>MTM1</t>
+  </si>
+  <si>
+    <t>TCF4</t>
+  </si>
+  <si>
+    <t>TNPO2</t>
+  </si>
+  <si>
+    <t>UBQLN2</t>
+  </si>
+  <si>
+    <t>WNT10A</t>
+  </si>
+  <si>
+    <t>FMO3</t>
+  </si>
+  <si>
+    <t>PPP3CA</t>
+  </si>
+  <si>
+    <t>KCNV2</t>
+  </si>
+  <si>
+    <t>C1R</t>
+  </si>
+  <si>
+    <t>SEC23B</t>
+  </si>
+  <si>
+    <t>SERPINA1</t>
+  </si>
+  <si>
+    <t>DKC1</t>
+  </si>
+  <si>
+    <t>LPAR6</t>
+  </si>
+  <si>
+    <t>PCCB</t>
+  </si>
+  <si>
+    <t>SLC1A2</t>
+  </si>
+  <si>
+    <t>EYA1</t>
+  </si>
+  <si>
+    <t>DBT</t>
+  </si>
+  <si>
+    <t>AIFM1</t>
+  </si>
+  <si>
+    <t>ANOS1</t>
+  </si>
+  <si>
+    <t>ATP6V1B2</t>
+  </si>
+  <si>
+    <t>COQ4</t>
+  </si>
+  <si>
+    <t>IL11RA</t>
+  </si>
+  <si>
+    <t>PRMT7</t>
+  </si>
+  <si>
+    <t>RARS1</t>
+  </si>
+  <si>
+    <t>XPC</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +423,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,152 +739,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R106"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>gene</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>n_pathogenic</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_benign</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_calm_weight</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_codon_rank</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_top_codon_weight_decile</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_cross_modal_gain</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_gain_rank</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>esm2_top_cross_modal_gain_decile</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_calm_weight</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_codon_rank</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_top_codon_weight_decile</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_gain_over_protein</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_gain_rank</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>esm1b_top_gain_decile</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>top_weight_both_plm_backgrounds</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>top_weight_and_gain_within_esm2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SH3BP2</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="n">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>16</v>
+      </c>
+      <c r="C2">
         <v>6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.968</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.3166666666666667</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.97</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.35</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>1</v>
       </c>
       <c r="P2" t="b">
@@ -578,52 +855,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MEF2C</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>20</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>21</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.966</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>4</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0.1023809523809522</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>21</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.98</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>1</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.0166666666666666</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>61</v>
       </c>
       <c r="P3" t="b">
@@ -636,52 +911,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GP1BA</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="n">
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
         <v>13</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>7</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.9360000000000001</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>7</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.06593406593406601</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>32</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.6980000000000001</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>24</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>-0.0109890109890109</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>341</v>
       </c>
       <c r="P4" t="b">
@@ -694,52 +967,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MMACHC</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
         <v>25</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>20</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.918</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>10</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>0.17</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>6</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.6759999999999999</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>30</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>-0.04</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>414</v>
       </c>
       <c r="P5" t="b">
@@ -752,52 +1023,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KCNH1</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
         <v>73</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>16</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>57</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.8460000000000001</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>15</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.0997807017543859</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>22</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.8160000000000001</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>10</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.0592105263157894</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>17</v>
       </c>
       <c r="P6" t="b">
@@ -810,52 +1079,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SOX5</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
         <v>28</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>16</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>12</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.8220000000000001</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>17</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.1041666666666667</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>20</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>0.9</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>3</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>0.03125</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>35</v>
       </c>
       <c r="P7" t="b">
@@ -868,52 +1135,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SOX9</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
         <v>49</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>30</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>19</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.7879999999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>20</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.0982456140350878</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>23</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>0.6979999999999998</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>26</v>
       </c>
       <c r="M8" t="b">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>0.1298245614035087</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>7</v>
       </c>
       <c r="P8" t="b">
@@ -926,52 +1191,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ADGRG1</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
         <v>21</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>9</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>12</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.786</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.0925925925925926</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>25</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>0.5900000000000001</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>47</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>-0.0833333333333333</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>454</v>
       </c>
       <c r="P9" t="b">
@@ -984,52 +1247,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MLH1</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
         <v>189</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>155</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>34</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.776</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>24</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.0603415559772295</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>34</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.734</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>20</v>
       </c>
       <c r="M10" t="b">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>0.0453510436432637</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>24</v>
       </c>
       <c r="P10" t="b">
@@ -1042,52 +1303,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GATA1</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11">
         <v>26</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>16</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.76</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>26</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.1437499999999999</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>10</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>0.784</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>14</v>
       </c>
       <c r="M11" t="b">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>0.0312499999999998</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>37</v>
       </c>
       <c r="P11" t="b">
@@ -1100,52 +1359,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>UROS</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
         <v>14</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.708</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>38</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.0833333333333333</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>27</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>0.756</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>18</v>
       </c>
       <c r="M12" t="b">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.110223024625156e-16</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="N12">
+        <v>1.110223024625156E-16</v>
+      </c>
+      <c r="O12">
         <v>116</v>
       </c>
       <c r="P12" t="b">
@@ -1158,52 +1415,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STING1</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13">
         <v>17</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.6759999999999999</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>43</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.0499999999999999</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>40</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>0.624</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>41</v>
       </c>
       <c r="M13" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>0.09999999999999989</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>9</v>
       </c>
       <c r="P13" t="b">
@@ -1216,52 +1471,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>FGFR3</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
         <v>49</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>32</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>17</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.6719999999999999</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>45</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>0.0533088235294118</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>36</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>0.674</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>31</v>
       </c>
       <c r="M14" t="b">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>-0.0036764705882352</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>308</v>
       </c>
       <c r="P14" t="b">
@@ -1274,52 +1527,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PAFAH1B1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
         <v>47</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>35</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>12</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.8959999999999999</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>12</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>0.0261904761904762</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>72</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>0.844</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>8</v>
       </c>
       <c r="M15" t="b">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>0.0142857142857142</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>66</v>
       </c>
       <c r="P15" t="b">
@@ -1332,52 +1583,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COL6A2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
         <v>95</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>51</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>44</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.806</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>18</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>0.0147058823529412</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>105</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>0.882</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>6</v>
       </c>
       <c r="M16" t="b">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>0.0334224598930481</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>32</v>
       </c>
       <c r="P16" t="b">
@@ -1390,52 +1639,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ROBO4</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
         <v>25</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>6</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>19</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.778</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>23</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0.0350877192982456</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>61</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>0.82</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>9</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>0.0263157894736841</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>42</v>
       </c>
       <c r="P17" t="b">
@@ -1448,52 +1695,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MLC1</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18">
         <v>23</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>6</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.748</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>32</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>-0.0294117647058823</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>413</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>0.6900000000000001</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>27</v>
       </c>
       <c r="M18" t="b">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>0.0490196078431373</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>23</v>
       </c>
       <c r="P18" t="b">
@@ -1506,52 +1751,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>POT1</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19">
         <v>14</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>5</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>9</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.6799999999999999</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>42</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>0.0222222222222222</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>79</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>0.73</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>21</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>0.0666666666666666</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>15</v>
       </c>
       <c r="P19" t="b">
@@ -1564,52 +1807,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>EMD</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
         <v>15</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>10</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.6679999999999999</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>46</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>0.0199999999999999</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>85</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>0.632</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>40</v>
       </c>
       <c r="M20" t="b">
         <v>1</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>0.0399999999999999</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>28</v>
       </c>
       <c r="P20" t="b">
@@ -1622,52 +1863,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FOXG1</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21">
         <v>145</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>75</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>70</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.976</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>0.12</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>17</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>0.418</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>110</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>-0.0017142857142857</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>291</v>
       </c>
       <c r="P21" t="b">
@@ -1680,52 +1919,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>IRF2BPL</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22">
         <v>18</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>5</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>13</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.976</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>2</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>0.2307692307692308</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>2</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
         <v>399</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>182</v>
       </c>
       <c r="P22" t="b">
@@ -1738,52 +1975,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>FOXP3</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
         <v>39</v>
       </c>
-      <c r="C23" t="n">
+      <c r="B23">
+        <v>39</v>
+      </c>
+      <c r="C23">
         <v>17</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>22</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.952</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>5</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>0.2058823529411764</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>0.4720000000000001</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>85</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>0.016042780748663</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>62</v>
       </c>
       <c r="P23" t="b">
@@ -1796,52 +2031,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TFE3</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24">
         <v>21</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>11</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>10</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.9379999999999999</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>6</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>0.2090909090909091</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>3</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>452</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>242</v>
       </c>
       <c r="P24" t="b">
@@ -1854,52 +2087,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FH</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25">
         <v>106</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>101</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.924</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>8</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>0.1683168316831683</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>7</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>0.208</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>229</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>-0.0039603960396039</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>313</v>
       </c>
       <c r="P25" t="b">
@@ -1912,52 +2143,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>EZH2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26">
         <v>49</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>27</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>22</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.918</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>9</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>0.1616161616161616</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>8</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>0.272</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>191</v>
       </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26">
         <v>-0.0016835016835016</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26">
         <v>290</v>
       </c>
       <c r="P26" t="b">
@@ -1970,52 +2199,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PTPN11</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27">
         <v>99</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>91</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>8</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.912</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>11</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>0.1057692307692308</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>19</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>0.286</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>184</v>
       </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27">
         <v>-0.0329670329670329</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27">
         <v>405</v>
       </c>
       <c r="P27" t="b">
@@ -2028,52 +2255,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PDE4D</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28">
         <v>22</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>13</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>9</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.8460000000000001</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>16</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>0.1538461538461537</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>9</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>422</v>
       </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>207</v>
       </c>
       <c r="P28" t="b">
@@ -2086,52 +2311,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>AFG3L2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29">
         <v>27</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>20</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>7</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.7899999999999999</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>19</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>0.05</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>39</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>0.462</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>89</v>
       </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29">
         <v>0.0428571428571429</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29">
         <v>26</v>
       </c>
       <c r="P29" t="b">
@@ -2144,52 +2367,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ASL</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30">
         <v>66</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>61</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>5</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.784</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>22</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>0.0524590163934426</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>37</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>0.458</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>91</v>
       </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30">
         <v>-0.0131147540983606</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30">
         <v>349</v>
       </c>
       <c r="P30" t="b">
@@ -2202,52 +2423,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>CNOT3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31">
         <v>16</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>8</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.7660000000000001</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>25</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>0.09375</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>24</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>0.144</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>267</v>
       </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>139</v>
       </c>
       <c r="P31" t="b">
@@ -2260,52 +2479,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>PCYT1A</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32">
         <v>20</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>6</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>14</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>0.756</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>28</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>0.1904761904761904</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>5</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>421</v>
       </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
         <v>206</v>
       </c>
       <c r="P32" t="b">
@@ -2318,52 +2535,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RALA</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33">
         <v>14</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>8</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>6</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>0.752</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>29</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>0.125</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>15</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>0.414</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>113</v>
       </c>
       <c r="M33" t="b">
         <v>0</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33">
         <v>0.0208333333333333</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33">
         <v>51</v>
       </c>
       <c r="P33" t="b">
@@ -2376,52 +2591,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PRKAG2</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
+    <row r="34" spans="1:18">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34">
         <v>27</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>17</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>10</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>0.7460000000000001</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>33</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>0.0470588235294118</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>42</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
         <v>429</v>
       </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
         <v>216</v>
       </c>
       <c r="P34" t="b">
@@ -2434,52 +2647,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RLIM</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35">
         <v>15</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>7</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>8</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>0.744</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>35</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>0.1428571428571429</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>12</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>432</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
         <v>219</v>
       </c>
       <c r="P35" t="b">
@@ -2492,52 +2703,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GARS1</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36">
         <v>28</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>17</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>11</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>0.71</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>37</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>0.1336898395721926</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>13</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>0.342</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>156</v>
       </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36">
         <v>-0.0106951871657754</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36">
         <v>338</v>
       </c>
       <c r="P36" t="b">
@@ -2550,52 +2759,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GPR143</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37">
         <v>25</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>14</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>11</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>0.698</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>39</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>0.0454545454545454</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>45</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>0.364</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>146</v>
       </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37">
         <v>-0.0714285714285714</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37">
         <v>442</v>
       </c>
       <c r="P37" t="b">
@@ -2608,52 +2815,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GFAP</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38">
         <v>55</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>47</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>0.696</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>40</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>0.0452127659574468</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>46</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38">
         <v>0.5600000000000001</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>55</v>
       </c>
       <c r="M38" t="b">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38">
         <v>0.007978723404255299</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38">
         <v>83</v>
       </c>
       <c r="P38" t="b">
@@ -2666,52 +2871,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CYP11B2</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39">
         <v>38</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>14</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>24</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>0.6719999999999999</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>44</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>0.050595238095238</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>38</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>0.026</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>329</v>
       </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39">
         <v>-0.0029761904761905</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39">
         <v>303</v>
       </c>
       <c r="P39" t="b">
@@ -2724,52 +2927,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>COL10A1</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40">
         <v>44</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>18</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>26</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>0.8560000000000001</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>13</v>
       </c>
       <c r="G40" t="b">
         <v>1</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>0.0363247863247863</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>59</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>0.254</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>209</v>
       </c>
       <c r="M40" t="b">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40">
         <v>-0.0064102564102563</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40">
         <v>323</v>
       </c>
       <c r="P40" t="b">
@@ -2782,52 +2983,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SPAST</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41">
         <v>137</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>123</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>14</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>0.8539999999999999</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>14</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>0.0394889663182346</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>52</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>0.066</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41">
         <v>311</v>
       </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41">
         <v>-0.0005807200929152</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41">
         <v>280</v>
       </c>
       <c r="P41" t="b">
@@ -2840,52 +3039,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TUBB2A</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42">
         <v>34</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>25</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>9</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>0.76</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>27</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>0.0399999999999999</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>49</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>0.458</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>95</v>
       </c>
       <c r="M42" t="b">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42">
         <v>-0.06666666666666669</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42">
         <v>441</v>
       </c>
       <c r="P42" t="b">
@@ -2898,52 +3095,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SLC6A1</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43">
         <v>107</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>53</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>54</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>0.75</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>30</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>0.0387840670859538</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>54</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>0.276</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>188</v>
       </c>
       <c r="M43" t="b">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43">
         <v>0.0031446540880502</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43">
         <v>96</v>
       </c>
       <c r="P43" t="b">
@@ -2956,52 +3151,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SPG7</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44">
         <v>24</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>16</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>8</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>0.75</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>31</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>0.0390625</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>53</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>0.304</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>170</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44">
         <v>-0.0078125</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44">
         <v>329</v>
       </c>
       <c r="P44" t="b">
@@ -3014,52 +3207,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>GNAO1</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45">
         <v>66</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>52</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>14</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>0.744</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>34</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>-0.0178571428571429</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>388</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45">
         <v>0.362</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>148</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45">
         <v>-0.0096153846153846</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45">
         <v>334</v>
       </c>
       <c r="P45" t="b">
@@ -3072,52 +3263,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SRD5A2</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46">
         <v>39</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>31</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>8</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>0.718</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>36</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>0.0282258064516128</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>68</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>0.302</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46">
         <v>171</v>
       </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N46">
         <v>-0.0201612903225806</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46">
         <v>376</v>
       </c>
       <c r="P46" t="b">
@@ -3130,52 +3319,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
+    <row r="47" spans="1:18">
+      <c r="A47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47">
         <v>128</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>99</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>29</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>41</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>0.0006966213862765</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>146</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>0.002</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>347</v>
       </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47">
         <v>-0.0010449320794149</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47">
         <v>283</v>
       </c>
       <c r="P47" t="b">
@@ -3188,52 +3375,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>WDR45</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
+    <row r="48" spans="1:18">
+      <c r="A48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48">
         <v>38</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>22</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>0.66</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>47</v>
       </c>
       <c r="G48" t="b">
         <v>1</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>0.0113636363636362</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>115</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>0.504</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48">
         <v>75</v>
       </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48">
         <v>0.03125</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48">
         <v>36</v>
       </c>
       <c r="P48" t="b">
@@ -3246,52 +3431,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MMUT</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+    <row r="49" spans="1:18">
+      <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49">
         <v>116</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>110</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>6</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>0.652</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>49</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>0.06818181818181809</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>31</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>0.1119999999999999</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>285</v>
       </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49">
         <v>0.0045454545454545</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49">
         <v>92</v>
       </c>
       <c r="P49" t="b">
@@ -3304,52 +3487,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>PORCN</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
+    <row r="50" spans="1:18">
+      <c r="A50" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50">
         <v>22</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>13</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>9</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>0.642</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>53</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>-0.0341880341880342</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>425</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50">
         <v>0.646</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>37</v>
       </c>
       <c r="M50" t="b">
         <v>1</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N50">
         <v>0.0256410256410255</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50">
         <v>43</v>
       </c>
       <c r="P50" t="b">
@@ -3362,52 +3543,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>MSH2</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
+    <row r="51" spans="1:18">
+      <c r="A51" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51">
         <v>341</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>109</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>232</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>0.5900000000000001</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>68</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>0.0472951597595697</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>41</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>0.708</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>23</v>
       </c>
       <c r="M51" t="b">
         <v>1</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N51">
         <v>0.0520404935147105</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51">
         <v>21</v>
       </c>
       <c r="P51" t="b">
@@ -3420,52 +3599,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>ALAS2</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
+    <row r="52" spans="1:18">
+      <c r="A52" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52">
         <v>21</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>15</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>6</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>0.588</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>69</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>0.0555555555555555</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>35</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>0.16</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52">
         <v>258</v>
       </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52">
         <v>-0.0555555555555555</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52">
         <v>433</v>
       </c>
       <c r="P52" t="b">
@@ -3478,52 +3655,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>FOXH1</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
+    <row r="53" spans="1:18">
+      <c r="A53" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53">
         <v>11</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>6</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>5</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>0.584</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>70</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>0.0333333333333333</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>64</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>0.742</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>19</v>
       </c>
       <c r="M53" t="b">
         <v>1</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
         <v>157</v>
       </c>
       <c r="P53" t="b">
@@ -3536,52 +3711,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
+    <row r="54" spans="1:18">
+      <c r="A54" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54">
         <v>171</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>61</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>110</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>0.58</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>71</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>0.0363636363636362</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>58</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>0.5959999999999999</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>46</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N54">
         <v>0.0366616989567808</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54">
         <v>31</v>
       </c>
       <c r="P54" t="b">
@@ -3594,52 +3767,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>KIF22</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
+    <row r="55" spans="1:18">
+      <c r="A55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55">
         <v>40</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>6</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>34</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>0.572</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>73</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>0.0686274509803922</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>30</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>0.5660000000000001</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55">
         <v>53</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N55">
         <v>0.0196078431372548</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55">
         <v>54</v>
       </c>
       <c r="P55" t="b">
@@ -3652,52 +3823,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>OPA1</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
+    <row r="56" spans="1:18">
+      <c r="A56" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56">
         <v>91</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>42</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>49</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>0.5639999999999999</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>78</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>0.0155490767735666</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>100</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>0.462</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56">
         <v>90</v>
       </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N56">
         <v>0.0281827016520894</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56">
         <v>39</v>
       </c>
       <c r="P56" t="b">
@@ -3710,52 +3879,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CNGB3</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57">
         <v>27</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>7</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>20</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>0.5599999999999999</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>79</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>-0.0214285714285713</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>401</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>0.6819999999999999</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>29</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N57">
         <v>-0.0428571428571429</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57">
         <v>417</v>
       </c>
       <c r="P57" t="b">
@@ -3768,52 +3935,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MTHFR</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58">
         <v>26</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>20</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>6</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>0.5520000000000002</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>82</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>0.075</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>29</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58">
         <v>0.226</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58">
         <v>225</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N58">
         <v>-0.0166666666666667</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58">
         <v>362</v>
       </c>
       <c r="P58" t="b">
@@ -3826,52 +3991,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>GATA2</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>75</v>
+      </c>
+      <c r="B59">
         <v>52</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>37</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>15</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>0.5459999999999999</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>83</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>0.09009009009009</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>26</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
         <v>382</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
         <v>163</v>
       </c>
       <c r="P59" t="b">
@@ -3884,52 +4047,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>KRIT1</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60">
         <v>13</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>5</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>8</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>0.538</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>84</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>-0.0749999999999999</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>453</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>0.658</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>34</v>
       </c>
       <c r="M60" t="b">
         <v>1</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N60">
         <v>-0.09999999999999989</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60">
         <v>461</v>
       </c>
       <c r="P60" t="b">
@@ -3942,52 +4103,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>DCLRE1C</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61">
         <v>25</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>13</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>12</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>0.532</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>87</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>0.0448717948717949</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>47</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>0.4019999999999999</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>118</v>
       </c>
       <c r="M61" t="b">
         <v>0</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N61">
         <v>-0.0320512820512821</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61">
         <v>402</v>
       </c>
       <c r="P61" t="b">
@@ -4000,52 +4159,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>PDE6C</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
+    <row r="62" spans="1:18">
+      <c r="A62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62">
         <v>16</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>11</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>5</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>0.528</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>88</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>0.1272727272727272</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>14</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62">
         <v>0.368</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>143</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N62">
         <v>0.018181818181818</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62">
         <v>55</v>
       </c>
       <c r="P62" t="b">
@@ -4058,52 +4215,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>PADI6</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63">
         <v>12</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>7</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>5</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>0.526</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>89</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>0.1428571428571429</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>11</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>0.136</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>271</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N63">
         <v>-0.0571428571428571</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63">
         <v>436</v>
       </c>
       <c r="P63" t="b">
@@ -4116,52 +4271,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>GLDC</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64">
         <v>90</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>78</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>12</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>0.5240000000000001</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>90</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>0.0779914529914528</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>28</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>0.344</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>155</v>
       </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N64">
         <v>-0.0512820512820513</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64">
         <v>430</v>
       </c>
       <c r="P64" t="b">
@@ -4174,52 +4327,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>LHCGR</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65">
         <v>17</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>12</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>5</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>0.524</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>91</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>0.0333333333333333</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>65</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K65">
         <v>0.784</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65">
         <v>15</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N65">
         <v>0.0666666666666666</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65">
         <v>14</v>
       </c>
       <c r="P65" t="b">
@@ -4232,52 +4383,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>PRSS1</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66">
         <v>22</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>7</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>15</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>0.5200000000000001</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>92</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>0.1238095238095237</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>16</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66">
         <v>0.506</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>74</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66">
         <v>-0.1142857142857144</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66">
         <v>463</v>
       </c>
       <c r="P66" t="b">
@@ -4290,52 +4439,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>GRIN1</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67">
         <v>97</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>61</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>36</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>0.514</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>96</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>0.0396174863387979</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>51</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>0.64</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>38</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67">
         <v>0.0573770491803279</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67">
         <v>18</v>
       </c>
       <c r="P67" t="b">
@@ -4348,52 +4495,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TP63</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
+    <row r="68" spans="1:18">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68">
         <v>68</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>57</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>11</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>0.506</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>97</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>0.0159489633173843</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>97</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K68">
         <v>0.614</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>43</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N68">
         <v>0.0287081339712917</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68">
         <v>38</v>
       </c>
       <c r="P68" t="b">
@@ -4406,52 +4551,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>CAMK2B</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
+    <row r="69" spans="1:18">
+      <c r="A69" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69">
         <v>62</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>5</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>57</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>0.502</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>99</v>
       </c>
       <c r="G69" t="b">
         <v>0</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>-0.0245614035087718</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>408</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>0.354</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>152</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N69">
         <v>0.0771929824561403</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69">
         <v>11</v>
       </c>
       <c r="P69" t="b">
@@ -4464,52 +4607,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>PPP2R5D</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
+    <row r="70" spans="1:18">
+      <c r="A70" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70">
         <v>18</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>13</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>5</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>0.49</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>101</v>
       </c>
       <c r="G70" t="b">
         <v>0</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>0.0461538461538462</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>43</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70">
         <v>0.7580000000000001</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70">
         <v>17</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N70">
         <v>0.0153846153846154</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70">
         <v>64</v>
       </c>
       <c r="P70" t="b">
@@ -4522,52 +4663,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>EPHB4</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
+    <row r="71" spans="1:18">
+      <c r="A71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71">
         <v>79</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>17</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>62</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>0.4859999999999999</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>103</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71">
         <v>0.0104364326375712</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>119</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>0.362</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>147</v>
       </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
-      <c r="N71" t="n">
+      <c r="N71">
         <v>0.0256166982922201</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71">
         <v>44</v>
       </c>
       <c r="P71" t="b">
@@ -4580,52 +4719,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>IL7R</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
+    <row r="72" spans="1:18">
+      <c r="A72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72">
         <v>26</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>9</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>17</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>0.482</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>107</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>-0.0130718954248365</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>369</v>
       </c>
       <c r="J72" t="b">
         <v>0</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>0.8080000000000001</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72">
         <v>11</v>
       </c>
       <c r="M72" t="b">
         <v>1</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N72">
         <v>0.0522875816993464</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72">
         <v>20</v>
       </c>
       <c r="P72" t="b">
@@ -4638,52 +4775,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>RAG2</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
+    <row r="73" spans="1:18">
+      <c r="A73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73">
         <v>58</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>49</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>9</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>0.48</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>108</v>
       </c>
       <c r="G73" t="b">
         <v>0</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>0.0226757369614513</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>75</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73">
         <v>0.57</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>52</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73">
         <v>0.0408163265306122</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73">
         <v>27</v>
       </c>
       <c r="P73" t="b">
@@ -4696,52 +4831,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>GPI</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74">
         <v>14</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>9</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>5</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>0.4640000000000001</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>110</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>0.0222222222222222</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>78</v>
       </c>
       <c r="J74" t="b">
         <v>0</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>0.62</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>42</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74">
         <v>-0.0222222222222222</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74">
         <v>381</v>
       </c>
       <c r="P74" t="b">
@@ -4754,52 +4887,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>HBB</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75">
         <v>35</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>27</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>8</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>0.4619999999999999</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>111</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>0.0185185185185184</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>88</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>0.53</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>63</v>
       </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N75">
         <v>0.0555555555555555</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75">
         <v>19</v>
       </c>
       <c r="P75" t="b">
@@ -4812,52 +4943,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>RPE65</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
+    <row r="76" spans="1:18">
+      <c r="A76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76">
         <v>84</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>78</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>6</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>0.444</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>123</v>
       </c>
       <c r="G76" t="b">
         <v>0</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>0.0149572649572649</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>103</v>
       </c>
       <c r="J76" t="b">
         <v>0</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>0.6679999999999999</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>32</v>
       </c>
       <c r="M76" t="b">
         <v>1</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
         <v>221</v>
       </c>
       <c r="P76" t="b">
@@ -4870,52 +4999,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>DNAI1</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
+    <row r="77" spans="1:18">
+      <c r="A77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77">
         <v>17</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>9</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>8</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>0.434</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>127</v>
       </c>
       <c r="G77" t="b">
         <v>0</v>
       </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
         <v>186</v>
       </c>
       <c r="J77" t="b">
         <v>0</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>0.2</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>234</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77">
         <v>0.0277777777777777</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77">
         <v>41</v>
       </c>
       <c r="P77" t="b">
@@ -4928,52 +5055,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>KCND2</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
+    <row r="78" spans="1:18">
+      <c r="A78" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78">
         <v>16</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>5</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>11</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>0.432</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>128</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>0.1090909090909089</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>18</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
         <v>401</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
         <v>184</v>
       </c>
       <c r="P78" t="b">
@@ -4986,52 +5111,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>CDH1</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
+    <row r="79" spans="1:18">
+      <c r="A79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B79">
         <v>106</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>17</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>89</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>0.406</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>136</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>-0.037673496364838</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>427</v>
       </c>
       <c r="J79" t="b">
         <v>0</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>0.898</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79">
         <v>4</v>
       </c>
       <c r="M79" t="b">
         <v>1</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79">
         <v>0.2227362855254461</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79">
         <v>2</v>
       </c>
       <c r="P79" t="b">
@@ -5044,52 +5167,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>MAK</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
+    <row r="80" spans="1:18">
+      <c r="A80" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80">
         <v>13</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>6</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>7</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>0.4</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>141</v>
       </c>
       <c r="G80" t="b">
         <v>0</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>-0.0238095238095239</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>406</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>0.544</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80">
         <v>58</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80">
         <v>0.0238095238095237</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80">
         <v>47</v>
       </c>
       <c r="P80" t="b">
@@ -5102,52 +5223,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ZMYND11</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
+    <row r="81" spans="1:18">
+      <c r="A81" t="s">
+        <v>97</v>
+      </c>
+      <c r="B81">
         <v>24</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>10</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>14</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>0.358</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>160</v>
       </c>
       <c r="G81" t="b">
         <v>0</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81">
         <v>0.0142857142857142</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>107</v>
       </c>
       <c r="J81" t="b">
         <v>0</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81">
         <v>0.788</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81">
         <v>13</v>
       </c>
       <c r="M81" t="b">
         <v>1</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81">
         <v>0.1857142857142858</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81">
         <v>3</v>
       </c>
       <c r="P81" t="b">
@@ -5160,52 +5279,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>MTM1</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
+    <row r="82" spans="1:18">
+      <c r="A82" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82">
         <v>72</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>49</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>23</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>0.35</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>162</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82">
         <v>-0.0035492457852706</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>327</v>
       </c>
       <c r="J82" t="b">
         <v>0</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82">
         <v>0.534</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82">
         <v>60</v>
       </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82">
         <v>0.0319432120674356</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82">
         <v>34</v>
       </c>
       <c r="P82" t="b">
@@ -5218,52 +5335,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TCF4</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
+    <row r="83" spans="1:18">
+      <c r="A83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B83">
         <v>84</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>40</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>44</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>0.344</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>164</v>
       </c>
       <c r="G83" t="b">
         <v>0</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83">
         <v>-0.0056818181818182</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>342</v>
       </c>
       <c r="J83" t="b">
         <v>0</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>0.66</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83">
         <v>33</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83">
         <v>0.0386363636363635</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O83">
         <v>30</v>
       </c>
       <c r="P83" t="b">
@@ -5276,52 +5391,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TNPO2</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
+    <row r="84" spans="1:18">
+      <c r="A84" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84">
         <v>11</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>6</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>5</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>0.336</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>167</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84">
         <v>-0.0333333333333333</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>421</v>
       </c>
       <c r="J84" t="b">
         <v>0</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84">
         <v>0.136</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84">
         <v>273</v>
       </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84">
         <v>0.06666666666666669</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84">
         <v>13</v>
       </c>
       <c r="P84" t="b">
@@ -5334,52 +5447,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>UBQLN2</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
+    <row r="85" spans="1:18">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85">
         <v>11</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>5</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>6</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>0.288</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>183</v>
       </c>
       <c r="G85" t="b">
         <v>0</v>
       </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
         <v>286</v>
       </c>
       <c r="J85" t="b">
         <v>0</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K85">
         <v>0.8860000000000001</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85">
         <v>5</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85">
         <v>0.1333333333333333</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85">
         <v>6</v>
       </c>
       <c r="P85" t="b">
@@ -5392,52 +5503,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>WNT10A</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
+    <row r="86" spans="1:18">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86">
         <v>25</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>16</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>9</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>0.264</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>194</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86">
         <v>-0.0416666666666667</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>431</v>
       </c>
       <c r="J86" t="b">
         <v>0</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>0.25</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86">
         <v>212</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86">
         <v>0.0624999999999998</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86">
         <v>16</v>
       </c>
       <c r="P86" t="b">
@@ -5450,52 +5559,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>FMO3</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
+    <row r="87" spans="1:18">
+      <c r="A87" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87">
         <v>27</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>16</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>11</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>0.258</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>199</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87">
         <v>0.0454545454545454</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>44</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87">
         <v>0.656</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87">
         <v>35</v>
       </c>
       <c r="M87" t="b">
         <v>1</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87">
         <v>-0.0284090909090909</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87">
         <v>398</v>
       </c>
       <c r="P87" t="b">
@@ -5508,52 +5615,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>PPP3CA</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
+    <row r="88" spans="1:18">
+      <c r="A88" t="s">
+        <v>104</v>
+      </c>
+      <c r="B88">
         <v>18</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>13</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>5</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>0.258</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>201</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88">
         <v>0.0615384615384614</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>33</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K88">
         <v>0.532</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88">
         <v>61</v>
       </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88">
         <v>-0.0615384615384615</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88">
         <v>438</v>
       </c>
       <c r="P88" t="b">
@@ -5566,52 +5671,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>KCNV2</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
+    <row r="89" spans="1:18">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89">
         <v>25</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>11</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>14</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>0.232</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>221</v>
       </c>
       <c r="G89" t="b">
         <v>0</v>
       </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
         <v>226</v>
       </c>
       <c r="J89" t="b">
         <v>0</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>0.8699999999999999</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89">
         <v>7</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89">
         <v>0.1038961038961039</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89">
         <v>8</v>
       </c>
       <c r="P89" t="b">
@@ -5624,52 +5727,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>C1R</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
+    <row r="90" spans="1:18">
+      <c r="A90" t="s">
+        <v>106</v>
+      </c>
+      <c r="B90">
         <v>23</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>12</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>11</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>0.22</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>228</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90">
         <v>-0.0075757575757575</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>350</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>0.6</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90">
         <v>45</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90">
         <v>-0.0454545454545453</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90">
         <v>422</v>
       </c>
       <c r="P90" t="b">
@@ -5682,52 +5783,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>SEC23B</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
+    <row r="91" spans="1:18">
+      <c r="A91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B91">
         <v>11</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>6</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>5</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>0.204</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>236</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91">
         <v>-0.0333333333333333</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>420</v>
       </c>
       <c r="J91" t="b">
         <v>0</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91">
         <v>0.1</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91">
         <v>290</v>
       </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91">
         <v>0.0333333333333333</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91">
         <v>33</v>
       </c>
       <c r="P91" t="b">
@@ -5740,52 +5839,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>SERPINA1</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
+    <row r="92" spans="1:18">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92">
         <v>50</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>9</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>41</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>0.204</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>237</v>
       </c>
       <c r="G92" t="b">
         <v>0</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92">
         <v>0.02710027100271</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>70</v>
       </c>
       <c r="J92" t="b">
         <v>0</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>0.5399999999999999</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92">
         <v>59</v>
       </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92">
         <v>0.0433604336043359</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92">
         <v>25</v>
       </c>
       <c r="P92" t="b">
@@ -5798,52 +5895,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>DKC1</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
+    <row r="93" spans="1:18">
+      <c r="A93" t="s">
+        <v>109</v>
+      </c>
+      <c r="B93">
         <v>20</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>14</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>6</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>0.174</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>250</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
       </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
         <v>185</v>
       </c>
       <c r="J93" t="b">
         <v>0</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>0.514</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93">
         <v>70</v>
       </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93">
         <v>0.0238095238095238</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93">
         <v>46</v>
       </c>
       <c r="P93" t="b">
@@ -5856,52 +5951,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LPAR6</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
+    <row r="94" spans="1:18">
+      <c r="A94" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94">
         <v>12</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>7</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>5</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>0.172</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>252</v>
       </c>
       <c r="G94" t="b">
         <v>0</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94">
         <v>-0.057142857142857</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>447</v>
       </c>
       <c r="J94" t="b">
         <v>0</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94">
         <v>0.652</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94">
         <v>36</v>
       </c>
       <c r="M94" t="b">
         <v>1</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94">
         <v>-0.057142857142857</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94">
         <v>435</v>
       </c>
       <c r="P94" t="b">
@@ -5914,52 +6007,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>PCCB</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
+    <row r="95" spans="1:18">
+      <c r="A95" t="s">
+        <v>111</v>
+      </c>
+      <c r="B95">
         <v>47</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>42</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>5</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>0.152</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>260</v>
       </c>
       <c r="G95" t="b">
         <v>0</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95">
         <v>-0.0095238095238094</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95">
         <v>358</v>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95">
         <v>0.718</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95">
         <v>22</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95">
         <v>-0.09523809523809521</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95">
         <v>456</v>
       </c>
       <c r="P95" t="b">
@@ -5972,52 +6063,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>SLC1A2</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
+    <row r="96" spans="1:18">
+      <c r="A96" t="s">
+        <v>112</v>
+      </c>
+      <c r="B96">
         <v>62</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>6</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>56</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>0.126</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>278</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96">
         <v>-0.0148809523809523</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96">
         <v>378</v>
       </c>
       <c r="J96" t="b">
         <v>0</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96">
         <v>0.608</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96">
         <v>44</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96">
         <v>-0.07142857142857149</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96">
         <v>444</v>
       </c>
       <c r="P96" t="b">
@@ -6030,52 +6119,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>EYA1</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
+    <row r="97" spans="1:18">
+      <c r="A97" t="s">
+        <v>113</v>
+      </c>
+      <c r="B97">
         <v>22</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>9</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>13</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>0.12</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>282</v>
       </c>
       <c r="G97" t="b">
         <v>0</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97">
         <v>0.017094017094017</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97">
         <v>93</v>
       </c>
       <c r="J97" t="b">
         <v>0</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97">
         <v>0.336</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97">
         <v>159</v>
       </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97">
         <v>0.0512820512820513</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O97">
         <v>22</v>
       </c>
       <c r="P97" t="b">
@@ -6088,52 +6175,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>DBT</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
+    <row r="98" spans="1:18">
+      <c r="A98" t="s">
+        <v>114</v>
+      </c>
+      <c r="B98">
         <v>24</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>16</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>8</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>0.112</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>287</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
         <v>184</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
-      <c r="K98" t="n">
+      <c r="K98">
         <v>0.6859999999999999</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98">
         <v>28</v>
       </c>
       <c r="M98" t="b">
         <v>1</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98">
         <v>-0.046875</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98">
         <v>423</v>
       </c>
       <c r="P98" t="b">
@@ -6146,52 +6231,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>AIFM1</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
+    <row r="99" spans="1:18">
+      <c r="A99" t="s">
+        <v>115</v>
+      </c>
+      <c r="B99">
         <v>31</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>16</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>15</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>0.098</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>292</v>
       </c>
       <c r="G99" t="b">
         <v>0</v>
       </c>
-      <c r="H99" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" t="n">
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
         <v>158</v>
       </c>
       <c r="J99" t="b">
         <v>0</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99">
         <v>0.634</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99">
         <v>39</v>
       </c>
       <c r="M99" t="b">
         <v>1</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99">
         <v>0.025</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99">
         <v>45</v>
       </c>
       <c r="P99" t="b">
@@ -6204,52 +6287,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ANOS1</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
+    <row r="100" spans="1:18">
+      <c r="A100" t="s">
+        <v>116</v>
+      </c>
+      <c r="B100">
         <v>17</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>7</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>10</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>0.066</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>313</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100">
         <v>0.0285714285714285</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100">
         <v>67</v>
       </c>
       <c r="J100" t="b">
         <v>0</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100">
         <v>0.36</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100">
         <v>150</v>
       </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100">
         <v>0.07142857142857149</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100">
         <v>12</v>
       </c>
       <c r="P100" t="b">
@@ -6262,52 +6343,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ATP6V1B2</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
+    <row r="101" spans="1:18">
+      <c r="A101" t="s">
+        <v>117</v>
+      </c>
+      <c r="B101">
         <v>12</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>6</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>6</v>
       </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
         <v>360</v>
       </c>
       <c r="G101" t="b">
         <v>0</v>
       </c>
-      <c r="H101" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" t="n">
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
         <v>164</v>
       </c>
       <c r="J101" t="b">
         <v>0</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K101">
         <v>0.074</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101">
         <v>301</v>
       </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101">
         <v>0.0277777777777777</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101">
         <v>40</v>
       </c>
       <c r="P101" t="b">
@@ -6320,52 +6399,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>COQ4</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
+    <row r="102" spans="1:18">
+      <c r="A102" t="s">
+        <v>118</v>
+      </c>
+      <c r="B102">
         <v>12</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>6</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>6</v>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
         <v>369</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
       </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
         <v>177</v>
       </c>
       <c r="J102" t="b">
         <v>0</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102">
         <v>0.3259999999999999</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102">
         <v>162</v>
       </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102">
         <v>0.1388888888888889</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102">
         <v>5</v>
       </c>
       <c r="P102" t="b">
@@ -6378,52 +6455,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>IL11RA</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
+    <row r="103" spans="1:18">
+      <c r="A103" t="s">
+        <v>119</v>
+      </c>
+      <c r="B103">
         <v>10</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>5</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>5</v>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
         <v>403</v>
       </c>
       <c r="G103" t="b">
         <v>0</v>
       </c>
-      <c r="H103" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" t="n">
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
         <v>222</v>
       </c>
       <c r="J103" t="b">
         <v>0</v>
       </c>
-      <c r="K103" t="n">
+      <c r="K103">
         <v>0.6980000000000001</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103">
         <v>25</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
       </c>
-      <c r="N103" t="n">
-        <v>-1.110223024625156e-16</v>
-      </c>
-      <c r="O103" t="n">
+      <c r="N103">
+        <v>-1.110223024625156E-16</v>
+      </c>
+      <c r="O103">
         <v>266</v>
       </c>
       <c r="P103" t="b">
@@ -6436,52 +6511,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>PRMT7</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
+    <row r="104" spans="1:18">
+      <c r="A104" t="s">
+        <v>120</v>
+      </c>
+      <c r="B104">
         <v>10</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>5</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>5</v>
       </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
         <v>427</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
       </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
         <v>251</v>
       </c>
       <c r="J104" t="b">
         <v>0</v>
       </c>
-      <c r="K104" t="n">
+      <c r="K104">
         <v>0.452</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104">
         <v>99</v>
       </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104">
         <v>0.0399999999999999</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104">
         <v>29</v>
       </c>
       <c r="P104" t="b">
@@ -6494,52 +6567,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>RARS1</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
+    <row r="105" spans="1:18">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+      <c r="B105">
         <v>12</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>7</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>5</v>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
         <v>431</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
       </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
         <v>254</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105">
         <v>0.7699999999999999</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105">
         <v>16</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N105">
         <v>0.1714285714285714</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O105">
         <v>4</v>
       </c>
       <c r="P105" t="b">
@@ -6552,52 +6623,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>XPC</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
+    <row r="106" spans="1:18">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106">
         <v>16</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>5</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>11</v>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
         <v>465</v>
       </c>
       <c r="G106" t="b">
         <v>0</v>
       </c>
-      <c r="H106" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" t="n">
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
         <v>290</v>
       </c>
       <c r="J106" t="b">
         <v>0</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106">
         <v>0.794</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106">
         <v>12</v>
       </c>
       <c r="M106" t="b">
         <v>1</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N106">
         <v>0.0909090909090908</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O106">
         <v>10</v>
       </c>
       <c r="P106" t="b">
@@ -6611,6 +6680,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>